--- a/data/gravel/Argon 18 Dark Matter 2025.xlsx
+++ b/data/gravel/Argon 18 Dark Matter 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF4FC30-5C49-7B4E-B6C0-78D592986643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85693E0-83B0-E041-8D7E-E5B9293BFE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1720" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27700" windowHeight="14380" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Argon 18 Dark Matter 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="118">
   <si>
     <t>model</t>
   </si>
@@ -128,12 +128,6 @@
     <t>material</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -288,13 +282,121 @@
   </si>
   <si>
     <t>a10:h37</t>
+  </si>
+  <si>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -363,6 +465,18 @@
       <color rgb="FF000000"/>
       <name val="Rift"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -384,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -393,12 +507,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5278,32 +5399,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3856DE37-3828-6849-A98A-EC05E320BDEE}">
-  <dimension ref="A1:AC119"/>
+  <dimension ref="A1:AH119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="29" width="12.83203125" style="1" customWidth="1"/>
+    <col min="30" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -5311,7 +5432,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:34">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -5319,57 +5440,225 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5" spans="1:34">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
-      <c r="A6" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" customFormat="1" ht="55" customHeight="1">
+      <c r="A6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="B6" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="S6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="T6" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="U6" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="V6" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="W6" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="X6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z6" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA6" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB6" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC6" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD6" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE6" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF6" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG6" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH6" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34">
       <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:29">
-      <c r="A8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-    </row>
-    <row r="9" spans="1:29">
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>57</v>
+      </c>
+      <c r="F7" s="1">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="1">
+        <v>142</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="1">
+        <v>27.2</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" s="1">
+        <v>44</v>
+      </c>
+      <c r="S7" s="1">
+        <v>48</v>
+      </c>
+      <c r="U7" s="1">
+        <v>3</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>3650</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+    </row>
+    <row r="9" spans="1:34">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
@@ -5388,53 +5677,53 @@
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
     </row>
-    <row r="10" spans="1:29" ht="24">
+    <row r="10" spans="1:34" ht="24">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="J10" s="3"/>
-      <c r="L10" s="11"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="R10" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="S10" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
@@ -5447,42 +5736,42 @@
       <c r="AB10" s="5"/>
       <c r="AC10" s="5"/>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11" spans="1:34">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="5">
-        <f>N11*10</f>
+        <f t="shared" ref="C11:H11" si="0">N11*10</f>
         <v>420</v>
       </c>
       <c r="D11" s="5">
-        <f>O11*10</f>
+        <f t="shared" si="0"/>
         <v>435</v>
       </c>
       <c r="E11" s="5">
-        <f>P11*10</f>
+        <f t="shared" si="0"/>
         <v>460</v>
       </c>
       <c r="F11" s="5">
-        <f>Q11*10</f>
+        <f t="shared" si="0"/>
         <v>495</v>
       </c>
       <c r="G11" s="5">
-        <f>R11*10</f>
+        <f t="shared" si="0"/>
         <v>540</v>
       </c>
       <c r="H11" s="5">
-        <f>S11*10</f>
+        <f t="shared" si="0"/>
         <v>585</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="12"/>
+      <c r="L11" s="11"/>
       <c r="M11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N11" s="5">
         <v>42</v>
@@ -5513,12 +5802,12 @@
       <c r="AB11" s="5"/>
       <c r="AC11" s="5"/>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" spans="1:34">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="5">
         <v>75.5</v>
@@ -5540,9 +5829,9 @@
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="12"/>
+      <c r="L12" s="11"/>
       <c r="M12" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N12" s="5">
         <v>75.5</v>
@@ -5573,12 +5862,12 @@
       <c r="AB12" s="5"/>
       <c r="AC12" s="5"/>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13" spans="1:34">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="5">
         <v>68.5</v>
@@ -5600,9 +5889,9 @@
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="12"/>
+      <c r="L13" s="11"/>
       <c r="M13" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N13" s="5">
         <v>68.5</v>
@@ -5633,42 +5922,42 @@
       <c r="AB13" s="5"/>
       <c r="AC13" s="5"/>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:34">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="5">
-        <f>N14*10</f>
+        <f t="shared" ref="C14:H20" si="1">N14*10</f>
         <v>507</v>
       </c>
       <c r="D14" s="5">
-        <f>O14*10</f>
+        <f t="shared" si="1"/>
         <v>530</v>
       </c>
       <c r="E14" s="5">
-        <f>P14*10</f>
+        <f t="shared" si="1"/>
         <v>553</v>
       </c>
       <c r="F14" s="5">
-        <f>Q14*10</f>
+        <f t="shared" si="1"/>
         <v>577</v>
       </c>
       <c r="G14" s="5">
-        <f>R14*10</f>
+        <f t="shared" si="1"/>
         <v>602</v>
       </c>
       <c r="H14" s="5">
-        <f>S14*10</f>
+        <f t="shared" si="1"/>
         <v>629</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="12"/>
+      <c r="L14" s="11"/>
       <c r="M14" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N14" s="5">
         <v>50.7</v>
@@ -5699,42 +5988,42 @@
       <c r="AB14" s="5"/>
       <c r="AC14" s="5"/>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:34">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="5">
-        <f>N15*10</f>
+        <f t="shared" si="1"/>
         <v>436</v>
       </c>
       <c r="D15" s="5">
-        <f>O15*10</f>
+        <f t="shared" si="1"/>
         <v>436</v>
       </c>
       <c r="E15" s="5">
-        <f>P15*10</f>
+        <f t="shared" si="1"/>
         <v>436</v>
       </c>
       <c r="F15" s="5">
-        <f>Q15*10</f>
+        <f t="shared" si="1"/>
         <v>436</v>
       </c>
       <c r="G15" s="5">
-        <f>R15*10</f>
+        <f t="shared" si="1"/>
         <v>436</v>
       </c>
       <c r="H15" s="5">
-        <f>S15*10</f>
+        <f t="shared" si="1"/>
         <v>436</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="12"/>
+      <c r="L15" s="11"/>
       <c r="M15" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N15" s="5">
         <v>43.6</v>
@@ -5765,42 +6054,42 @@
       <c r="AB15" s="5"/>
       <c r="AC15" s="5"/>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16" spans="1:34">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="5">
-        <f>N16*10</f>
+        <f t="shared" si="1"/>
         <v>1030</v>
       </c>
       <c r="D16" s="5">
-        <f>O16*10</f>
+        <f t="shared" si="1"/>
         <v>1036</v>
       </c>
       <c r="E16" s="5">
-        <f>P16*10</f>
+        <f t="shared" si="1"/>
         <v>1045</v>
       </c>
       <c r="F16" s="5">
-        <f>Q16*10</f>
+        <f t="shared" si="1"/>
         <v>1059</v>
       </c>
       <c r="G16" s="5">
-        <f>R16*10</f>
+        <f t="shared" si="1"/>
         <v>1080</v>
       </c>
       <c r="H16" s="5">
-        <f>S16*10</f>
+        <f t="shared" si="1"/>
         <v>1101</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="6"/>
       <c r="M16" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N16" s="3">
         <v>103</v>
@@ -5832,37 +6121,37 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="5">
-        <f>N17*10</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="D17" s="5">
-        <f>O17*10</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="E17" s="5">
-        <f>P17*10</f>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="F17" s="5">
-        <f>Q17*10</f>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="G17" s="5">
-        <f>R17*10</f>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="H17" s="5">
-        <f>S17*10</f>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17"/>
       <c r="M17" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N17" s="3">
         <v>8</v>
@@ -5888,37 +6177,37 @@
         <v>9</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" s="5">
-        <f>N18*10</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="D18" s="5">
-        <f>O18*10</f>
+        <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="E18" s="5">
-        <f>P18*10</f>
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="F18" s="5">
-        <f>Q18*10</f>
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="G18" s="5">
-        <f>R18*10</f>
+        <f t="shared" si="1"/>
         <v>151</v>
       </c>
       <c r="H18" s="5">
-        <f>S18*10</f>
+        <f t="shared" si="1"/>
         <v>178</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18"/>
       <c r="M18" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N18" s="3">
         <v>7.2</v>
@@ -5941,40 +6230,40 @@
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="5">
-        <f>N19*10</f>
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="D19" s="5">
-        <f>O19*10</f>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="E19" s="5">
-        <f>P19*10</f>
+        <f t="shared" si="1"/>
         <v>131</v>
       </c>
       <c r="F19" s="5">
-        <f>Q19*10</f>
+        <f t="shared" si="1"/>
         <v>151</v>
       </c>
       <c r="G19" s="5">
-        <f>R19*10</f>
+        <f t="shared" si="1"/>
         <v>176</v>
       </c>
       <c r="H19" s="5">
-        <f>S19*10</f>
+        <f t="shared" si="1"/>
         <v>203</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19"/>
       <c r="M19" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N19" s="3">
         <v>9.5</v>
@@ -6000,36 +6289,36 @@
         <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C20" s="5">
-        <f>N20*10</f>
+        <f t="shared" si="1"/>
         <v>713</v>
       </c>
       <c r="D20" s="5">
-        <f>O20*10</f>
+        <f t="shared" si="1"/>
         <v>729</v>
       </c>
       <c r="E20" s="5">
-        <f>P20*10</f>
+        <f t="shared" si="1"/>
         <v>755</v>
       </c>
       <c r="F20" s="5">
-        <f>Q20*10</f>
+        <f t="shared" si="1"/>
         <v>786</v>
       </c>
       <c r="G20" s="5">
-        <f>R20*10</f>
+        <f t="shared" si="1"/>
         <v>825</v>
       </c>
       <c r="H20" s="5">
-        <f>S20*10</f>
+        <f t="shared" si="1"/>
         <v>863</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20"/>
       <c r="M20" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N20" s="3">
         <v>71.3</v>
@@ -6055,35 +6344,35 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C21" s="5">
-        <f>N21</f>
+        <f t="shared" ref="C21:H21" si="2">N21</f>
         <v>425</v>
       </c>
       <c r="D21" s="5">
-        <f>O21</f>
+        <f t="shared" si="2"/>
         <v>425</v>
       </c>
       <c r="E21" s="5">
-        <f>P21</f>
+        <f t="shared" si="2"/>
         <v>425</v>
       </c>
       <c r="F21" s="5">
-        <f>Q21</f>
+        <f t="shared" si="2"/>
         <v>425</v>
       </c>
       <c r="G21" s="5">
-        <f>R21</f>
+        <f t="shared" si="2"/>
         <v>425</v>
       </c>
       <c r="H21" s="5">
-        <f>S21</f>
+        <f t="shared" si="2"/>
         <v>425</v>
       </c>
       <c r="L21"/>
       <c r="M21" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N21" s="1">
         <v>425</v>
@@ -6109,7 +6398,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="5">
         <v>54</v>
@@ -6131,7 +6420,7 @@
       </c>
       <c r="L22"/>
       <c r="M22" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N22" s="1">
         <v>54</v>
@@ -6157,35 +6446,35 @@
         <v>17</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C23" s="5">
-        <f>N23*10</f>
+        <f t="shared" ref="C23:H29" si="3">N23*10</f>
         <v>86</v>
       </c>
       <c r="D23" s="5">
-        <f>O23*10</f>
+        <f t="shared" si="3"/>
         <v>76</v>
       </c>
       <c r="E23" s="5">
-        <f>P23*10</f>
+        <f t="shared" si="3"/>
         <v>79</v>
       </c>
       <c r="F23" s="5">
-        <f>Q23*10</f>
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="G23" s="5">
-        <f>R23*10</f>
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="H23" s="5">
-        <f>S23*10</f>
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="L23"/>
       <c r="M23" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N23" s="1">
         <v>8.6</v>
@@ -6211,35 +6500,35 @@
         <v>8</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C24" s="5">
-        <f>N24*10</f>
+        <f t="shared" si="3"/>
         <v>520</v>
       </c>
       <c r="D24" s="5">
-        <f>O24*10</f>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="E24" s="5">
-        <f>P24*10</f>
+        <f t="shared" si="3"/>
         <v>561</v>
       </c>
       <c r="F24" s="5">
-        <f>Q24*10</f>
+        <f t="shared" si="3"/>
         <v>582</v>
       </c>
       <c r="G24" s="5">
-        <f>R24*10</f>
+        <f t="shared" si="3"/>
         <v>603</v>
       </c>
       <c r="H24" s="5">
-        <f>S24*10</f>
+        <f t="shared" si="3"/>
         <v>629</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N24" s="1">
         <v>52</v>
@@ -6262,38 +6551,38 @@
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C25" s="5">
-        <f>N25*10</f>
+        <f t="shared" si="3"/>
         <v>543</v>
       </c>
       <c r="D25" s="5">
-        <f>O25*10</f>
+        <f t="shared" si="3"/>
         <v>564</v>
       </c>
       <c r="E25" s="5">
-        <f>P25*10</f>
+        <f t="shared" si="3"/>
         <v>585</v>
       </c>
       <c r="F25" s="5">
-        <f>Q25*10</f>
+        <f t="shared" si="3"/>
         <v>606</v>
       </c>
       <c r="G25" s="5">
-        <f>R25*10</f>
+        <f t="shared" si="3"/>
         <v>627</v>
       </c>
       <c r="H25" s="5">
-        <f>S25*10</f>
+        <f t="shared" si="3"/>
         <v>653</v>
       </c>
       <c r="L25"/>
       <c r="M25" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N25" s="1">
         <v>54.3</v>
@@ -6319,35 +6608,35 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="5">
-        <f>N26*10</f>
+        <f t="shared" si="3"/>
         <v>370</v>
       </c>
       <c r="D26" s="5">
-        <f>O26*10</f>
+        <f t="shared" si="3"/>
         <v>382</v>
       </c>
       <c r="E26" s="5">
-        <f>P26*10</f>
+        <f t="shared" si="3"/>
         <v>394</v>
       </c>
       <c r="F26" s="5">
-        <f>Q26*10</f>
+        <f t="shared" si="3"/>
         <v>406</v>
       </c>
       <c r="G26" s="5">
-        <f>R26*10</f>
+        <f t="shared" si="3"/>
         <v>418</v>
       </c>
       <c r="H26" s="5">
-        <f>S26*10</f>
+        <f t="shared" si="3"/>
         <v>430</v>
       </c>
       <c r="L26"/>
       <c r="M26" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N26" s="1">
         <v>37</v>
@@ -6370,38 +6659,38 @@
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C27" s="5">
-        <f>N27*10</f>
+        <f t="shared" si="3"/>
         <v>361</v>
       </c>
       <c r="D27" s="5">
-        <f>O27*10</f>
+        <f t="shared" si="3"/>
         <v>373</v>
       </c>
       <c r="E27" s="5">
-        <f>P27*10</f>
+        <f t="shared" si="3"/>
         <v>386</v>
       </c>
       <c r="F27" s="5">
-        <f>Q27*10</f>
+        <f t="shared" si="3"/>
         <v>398</v>
       </c>
       <c r="G27" s="5">
-        <f>R27*10</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="H27" s="5">
-        <f>S27*10</f>
+        <f t="shared" si="3"/>
         <v>422</v>
       </c>
       <c r="L27"/>
       <c r="M27" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N27" s="1">
         <v>36.1</v>
@@ -6424,38 +6713,38 @@
     </row>
     <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C28" s="5">
-        <f>N28*10</f>
+        <f t="shared" si="3"/>
         <v>590</v>
       </c>
       <c r="D28" s="5">
-        <f>O28*10</f>
+        <f t="shared" si="3"/>
         <v>605</v>
       </c>
       <c r="E28" s="5">
-        <f>P28*10</f>
+        <f t="shared" si="3"/>
         <v>630</v>
       </c>
       <c r="F28" s="5">
-        <f>Q28*10</f>
+        <f t="shared" si="3"/>
         <v>665</v>
       </c>
       <c r="G28" s="5">
-        <f>R28*10</f>
+        <f t="shared" si="3"/>
         <v>710</v>
       </c>
       <c r="H28" s="5">
-        <f>S28*10</f>
+        <f t="shared" si="3"/>
         <v>755</v>
       </c>
       <c r="L28"/>
       <c r="M28" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N28" s="1">
         <v>59</v>
@@ -6478,38 +6767,38 @@
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C29" s="5">
-        <f>N29*10</f>
+        <f t="shared" si="3"/>
         <v>790</v>
       </c>
       <c r="D29" s="5">
-        <f>O29*10</f>
+        <f t="shared" si="3"/>
         <v>805</v>
       </c>
       <c r="E29" s="5">
-        <f>P29*10</f>
+        <f t="shared" si="3"/>
         <v>830</v>
       </c>
       <c r="F29" s="5">
-        <f>Q29*10</f>
+        <f t="shared" si="3"/>
         <v>865</v>
       </c>
       <c r="G29" s="5">
-        <f>R29*10</f>
+        <f t="shared" si="3"/>
         <v>910</v>
       </c>
       <c r="H29" s="5">
-        <f>S29*10</f>
+        <f t="shared" si="3"/>
         <v>955</v>
       </c>
       <c r="L29"/>
       <c r="M29" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N29" s="1">
         <v>79</v>
@@ -6538,10 +6827,10 @@
         <v>18</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="N30" s="8"/>
+      <c r="M30" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N30" s="15"/>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="1" t="s">
@@ -6569,11 +6858,11 @@
         <v>110</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="N31" s="13" t="s">
-        <v>70</v>
+      <c r="M31" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -6584,11 +6873,11 @@
         <v>20</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>72</v>
+      <c r="M32" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -6617,11 +6906,11 @@
         <v>700</v>
       </c>
       <c r="L33" s="6"/>
-      <c r="M33" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>73</v>
+      <c r="M33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -6650,11 +6939,11 @@
         <v>50</v>
       </c>
       <c r="L34"/>
-      <c r="M34" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>74</v>
+      <c r="M34" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -6682,11 +6971,11 @@
       <c r="H35" s="7">
         <v>57</v>
       </c>
-      <c r="M35" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>75</v>
+      <c r="M35" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -6714,11 +7003,11 @@
       <c r="H36" s="7">
         <v>195</v>
       </c>
-      <c r="M36" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N36" s="10" t="s">
-        <v>76</v>
+      <c r="M36" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -6746,11 +7035,11 @@
       <c r="H37" s="7">
         <v>200</v>
       </c>
-      <c r="M37" s="9" t="s">
+      <c r="M37" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N37" s="10" t="s">
-        <v>77</v>
+      <c r="N37" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -7000,8 +7289,7 @@
       <c r="L119"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="N8:AC8"/>
+  <mergeCells count="1">
     <mergeCell ref="M30:N30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Argon 18 Dark Matter 2025.xlsx
+++ b/data/gravel/Argon 18 Dark Matter 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9C22B1-1F70-EE46-A3AA-C3183121BEAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8931E59-8177-E840-92F6-6EABAD46EFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5840" yWindow="760" windowWidth="25100" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -1556,24 +1556,15 @@
       <c r="A47" t="s">
         <v>79</v>
       </c>
-      <c r="B47" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>81</v>
       </c>
-      <c r="B48" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>82</v>
-      </c>
-      <c r="B49" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Argon 18 Dark Matter 2025.xlsx
+++ b/data/gravel/Argon 18 Dark Matter 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8931E59-8177-E840-92F6-6EABAD46EFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38BFDC8-387D-8747-8FC5-5620CF8318E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5840" yWindow="760" windowWidth="25100" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3700" yWindow="760" windowWidth="25100" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://storage.googleapis.com/argon18craft/products/2025/Dark-Matter/DM.M.373B.2E.1_side-root-beer.png</t>
   </si>
 </sst>
 </file>
@@ -775,6 +778,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Argon 18 Dark Matter 2025.xlsx
+++ b/data/gravel/Argon 18 Dark Matter 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38BFDC8-387D-8747-8FC5-5620CF8318E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142ADC4E-1562-094A-877E-1C2169FDD62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3700" yWindow="760" windowWidth="25100" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -379,9 +379,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -401,17 +398,32 @@
   </si>
   <si>
     <t>https://storage.googleapis.com/argon18craft/products/2025/Dark-Matter/DM.M.373B.2E.1_side-root-beer.png</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Montreal, Quebec, Canada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -434,8 +446,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -732,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -780,7 +793,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1493,26 +1506,26 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" t="s">
         <v>120</v>
-      </c>
-      <c r="B38" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" t="s">
         <v>122</v>
-      </c>
-      <c r="B39" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" t="s">
         <v>124</v>
-      </c>
-      <c r="B40" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1758,8 +1771,16 @@
       <c r="A75" t="s">
         <v>118</v>
       </c>
-      <c r="B75" t="s">
-        <v>119</v>
+      <c r="B75" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>127</v>
+      </c>
+      <c r="B76" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Argon 18 Dark Matter 2025.xlsx
+++ b/data/gravel/Argon 18 Dark Matter 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142ADC4E-1562-094A-877E-1C2169FDD62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580D147F-AB85-D64C-8A01-C32D9FCFE590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3700" yWindow="760" windowWidth="25100" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="135">
   <si>
     <t>brand</t>
   </si>
@@ -407,6 +407,24 @@
   </si>
   <si>
     <t>Montreal, Quebec, Canada</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -745,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1606,131 +1624,113 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>87</v>
-      </c>
-      <c r="B52" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>90</v>
-      </c>
-      <c r="B54" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>92</v>
-      </c>
-      <c r="B55" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>93</v>
-      </c>
-      <c r="B56" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>95</v>
-      </c>
-      <c r="B57" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>87</v>
+      </c>
+      <c r="B58" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>90</v>
+      </c>
+      <c r="B60" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B62" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>104</v>
-      </c>
-      <c r="B64" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>105</v>
-      </c>
-      <c r="B65" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>107</v>
-      </c>
-      <c r="B66" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B69" t="s">
         <v>71</v>
@@ -1738,48 +1738,96 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>112</v>
+        <v>104</v>
+      </c>
+      <c r="B70" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>114</v>
+        <v>107</v>
+      </c>
+      <c r="B72" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B73" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>117</v>
+        <v>110</v>
+      </c>
+      <c r="B74" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>118</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>126</v>
+        <v>111</v>
+      </c>
+      <c r="B75" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>113</v>
+      </c>
+      <c r="B77" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B79" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>118</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>127</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B82" t="s">
         <v>128</v>
       </c>
     </row>

--- a/data/gravel/Argon 18 Dark Matter 2025.xlsx
+++ b/data/gravel/Argon 18 Dark Matter 2025.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580D147F-AB85-D64C-8A01-C32D9FCFE590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC893F3-0A85-1C4D-95AC-F23EDEC30B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3700" yWindow="760" windowWidth="25100" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30480" yWindow="-28300" windowWidth="33620" windowHeight="20020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="164">
   <si>
     <t>brand</t>
   </si>
@@ -425,6 +438,93 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>Measure</t>
+  </si>
+  <si>
+    <t>XXS</t>
+  </si>
+  <si>
+    <t>XS</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>seat_tube_height_cm</t>
+  </si>
+  <si>
+    <t>seat_tube_angle_deg</t>
+  </si>
+  <si>
+    <t>head_tube_angle_deg</t>
+  </si>
+  <si>
+    <t>top_tube_length_cm</t>
+  </si>
+  <si>
+    <t>chainstay_length_cm</t>
+  </si>
+  <si>
+    <t>wheelbase_cm</t>
+  </si>
+  <si>
+    <t>bb_drop_cm</t>
+  </si>
+  <si>
+    <t>stand_over_height_cm</t>
+  </si>
+  <si>
+    <t>saddle_height_min_cm</t>
+  </si>
+  <si>
+    <t>saddle_height_max_cm</t>
+  </si>
+  <si>
+    <t>headtube_length_3d0_cm</t>
+  </si>
+  <si>
+    <t>headtube_length_3d35_cm</t>
+  </si>
+  <si>
+    <t>fork_length_axle_to_crown_cm</t>
+  </si>
+  <si>
+    <t>fork_rake_cm</t>
+  </si>
+  <si>
+    <t>trail_cm</t>
+  </si>
+  <si>
+    <t>stack_min_cm</t>
+  </si>
+  <si>
+    <t>stack_max_3d35_cm</t>
+  </si>
+  <si>
+    <t>reach_cm</t>
+  </si>
+  <si>
+    <t>reach_3d35_cm</t>
+  </si>
+  <si>
+    <t>layback</t>
+  </si>
+  <si>
+    <t>ett</t>
+  </si>
+  <si>
+    <t>stt</t>
   </si>
 </sst>
 </file>
@@ -763,13 +863,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -777,7 +877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -785,7 +885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -793,7 +893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -801,7 +901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -809,20 +909,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -847,8 +950,29 @@
       <c r="H8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J8" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" t="s">
+        <v>136</v>
+      </c>
+      <c r="L8" t="s">
+        <v>137</v>
+      </c>
+      <c r="M8" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" t="s">
+        <v>139</v>
+      </c>
+      <c r="O8" t="s">
+        <v>140</v>
+      </c>
+      <c r="P8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -856,25 +980,52 @@
         <v>21</v>
       </c>
       <c r="C9">
+        <f>K9*10</f>
         <v>420</v>
       </c>
       <c r="D9">
+        <f t="shared" ref="D9:H9" si="0">L9*10</f>
         <v>435</v>
       </c>
       <c r="E9">
+        <f t="shared" si="0"/>
         <v>460</v>
       </c>
       <c r="F9">
+        <f t="shared" si="0"/>
         <v>495</v>
       </c>
       <c r="G9">
+        <f t="shared" si="0"/>
         <v>540</v>
       </c>
       <c r="H9">
+        <f t="shared" si="0"/>
         <v>585</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K9">
+        <v>42</v>
+      </c>
+      <c r="L9">
+        <v>43.5</v>
+      </c>
+      <c r="M9">
+        <v>46</v>
+      </c>
+      <c r="N9">
+        <v>49.5</v>
+      </c>
+      <c r="O9">
+        <v>54</v>
+      </c>
+      <c r="P9">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -882,25 +1033,52 @@
         <v>23</v>
       </c>
       <c r="C10">
+        <f>K10</f>
         <v>75.5</v>
       </c>
       <c r="D10">
+        <f t="shared" ref="D10:H11" si="1">L10</f>
+        <v>74.900000000000006</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>74.3</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>73.7</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>73.099999999999994</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>72.5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K10">
         <v>75.5</v>
       </c>
-      <c r="E10">
-        <v>75.5</v>
-      </c>
-      <c r="F10">
-        <v>75.5</v>
-      </c>
-      <c r="G10">
-        <v>75.5</v>
-      </c>
-      <c r="H10">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L10">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="M10">
+        <v>74.3</v>
+      </c>
+      <c r="N10">
+        <v>73.7</v>
+      </c>
+      <c r="O10">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="P10">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -908,25 +1086,52 @@
         <v>25</v>
       </c>
       <c r="C11">
+        <f>K11</f>
         <v>68.5</v>
       </c>
       <c r="D11">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>70.5</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="J11" t="s">
+        <v>144</v>
+      </c>
+      <c r="K11">
         <v>68.5</v>
       </c>
-      <c r="E11">
-        <v>68.5</v>
-      </c>
-      <c r="F11">
-        <v>68.5</v>
-      </c>
-      <c r="G11">
-        <v>68.5</v>
-      </c>
-      <c r="H11">
-        <v>68.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L11">
+        <v>70</v>
+      </c>
+      <c r="M11">
+        <v>70.5</v>
+      </c>
+      <c r="N11">
+        <v>71</v>
+      </c>
+      <c r="O11">
+        <v>71</v>
+      </c>
+      <c r="P11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -934,25 +1139,52 @@
         <v>27</v>
       </c>
       <c r="C12">
+        <f t="shared" ref="C10:C27" si="2">K12*10</f>
         <v>507</v>
       </c>
       <c r="D12">
+        <f t="shared" ref="D12:D27" si="3">L12*10</f>
         <v>530</v>
       </c>
       <c r="E12">
+        <f t="shared" ref="E12:E27" si="4">M12*10</f>
         <v>553</v>
       </c>
       <c r="F12">
+        <f t="shared" ref="F12:F27" si="5">N12*10</f>
         <v>577</v>
       </c>
       <c r="G12">
+        <f t="shared" ref="G12:G27" si="6">O12*10</f>
         <v>602</v>
       </c>
       <c r="H12">
+        <f t="shared" ref="H12:H27" si="7">P12*10</f>
         <v>629</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J12" t="s">
+        <v>145</v>
+      </c>
+      <c r="K12">
+        <v>50.7</v>
+      </c>
+      <c r="L12">
+        <v>53</v>
+      </c>
+      <c r="M12">
+        <v>55.3</v>
+      </c>
+      <c r="N12">
+        <v>57.7</v>
+      </c>
+      <c r="O12">
+        <v>60.2</v>
+      </c>
+      <c r="P12">
+        <v>62.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -960,25 +1192,52 @@
         <v>29</v>
       </c>
       <c r="C13">
+        <f t="shared" si="2"/>
         <v>436</v>
       </c>
       <c r="D13">
+        <f t="shared" si="3"/>
         <v>436</v>
       </c>
       <c r="E13">
+        <f t="shared" si="4"/>
         <v>436</v>
       </c>
       <c r="F13">
+        <f t="shared" si="5"/>
         <v>436</v>
       </c>
       <c r="G13">
+        <f t="shared" si="6"/>
         <v>436</v>
       </c>
       <c r="H13">
+        <f t="shared" si="7"/>
         <v>436</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J13" t="s">
+        <v>146</v>
+      </c>
+      <c r="K13">
+        <v>43.6</v>
+      </c>
+      <c r="L13">
+        <v>43.6</v>
+      </c>
+      <c r="M13">
+        <v>43.6</v>
+      </c>
+      <c r="N13">
+        <v>43.6</v>
+      </c>
+      <c r="O13">
+        <v>43.6</v>
+      </c>
+      <c r="P13">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -986,25 +1245,52 @@
         <v>31</v>
       </c>
       <c r="C14">
+        <f t="shared" si="2"/>
         <v>1030</v>
       </c>
       <c r="D14">
+        <f t="shared" si="3"/>
         <v>1036</v>
       </c>
       <c r="E14">
+        <f t="shared" si="4"/>
         <v>1045</v>
       </c>
       <c r="F14">
+        <f t="shared" si="5"/>
         <v>1059</v>
       </c>
       <c r="G14">
+        <f t="shared" si="6"/>
         <v>1080</v>
       </c>
       <c r="H14">
+        <f t="shared" si="7"/>
         <v>1101</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J14" t="s">
+        <v>147</v>
+      </c>
+      <c r="K14">
+        <v>103</v>
+      </c>
+      <c r="L14">
+        <v>103.6</v>
+      </c>
+      <c r="M14">
+        <v>104.5</v>
+      </c>
+      <c r="N14">
+        <v>105.9</v>
+      </c>
+      <c r="O14">
+        <v>108</v>
+      </c>
+      <c r="P14">
+        <v>110.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1012,25 +1298,52 @@
         <v>33</v>
       </c>
       <c r="C15">
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="D15">
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="E15">
+        <f t="shared" si="4"/>
         <v>78</v>
       </c>
       <c r="F15">
+        <f t="shared" si="5"/>
         <v>78</v>
       </c>
       <c r="G15">
+        <f t="shared" si="6"/>
         <v>76</v>
       </c>
       <c r="H15">
+        <f t="shared" si="7"/>
         <v>76</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J15" t="s">
+        <v>148</v>
+      </c>
+      <c r="K15">
+        <v>8</v>
+      </c>
+      <c r="L15">
+        <v>8</v>
+      </c>
+      <c r="M15">
+        <v>7.8</v>
+      </c>
+      <c r="N15">
+        <v>7.8</v>
+      </c>
+      <c r="O15">
+        <v>7.6</v>
+      </c>
+      <c r="P15">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1038,25 +1351,52 @@
         <v>35</v>
       </c>
       <c r="C16">
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="D16">
+        <f t="shared" si="3"/>
         <v>87</v>
       </c>
       <c r="E16">
+        <f t="shared" si="4"/>
         <v>106</v>
       </c>
       <c r="F16">
+        <f t="shared" si="5"/>
         <v>126</v>
       </c>
       <c r="G16">
+        <f t="shared" si="6"/>
         <v>151</v>
       </c>
       <c r="H16">
+        <f t="shared" si="7"/>
         <v>178</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J16" t="s">
+        <v>152</v>
+      </c>
+      <c r="K16">
+        <v>7.2</v>
+      </c>
+      <c r="L16">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="M16">
+        <v>10.6</v>
+      </c>
+      <c r="N16">
+        <v>12.6</v>
+      </c>
+      <c r="O16">
+        <v>15.1</v>
+      </c>
+      <c r="P16">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -1064,25 +1404,52 @@
         <v>37</v>
       </c>
       <c r="C17">
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="D17">
+        <f t="shared" si="3"/>
         <v>112</v>
       </c>
       <c r="E17">
+        <f t="shared" si="4"/>
         <v>131</v>
       </c>
       <c r="F17">
+        <f t="shared" si="5"/>
         <v>151</v>
       </c>
       <c r="G17">
+        <f t="shared" si="6"/>
         <v>176</v>
       </c>
       <c r="H17">
+        <f t="shared" si="7"/>
         <v>203</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J17" t="s">
+        <v>153</v>
+      </c>
+      <c r="K17">
+        <v>9.5</v>
+      </c>
+      <c r="L17">
+        <v>11.2</v>
+      </c>
+      <c r="M17">
+        <v>13.1</v>
+      </c>
+      <c r="N17">
+        <v>15.1</v>
+      </c>
+      <c r="O17">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="P17">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -1090,25 +1457,52 @@
         <v>39</v>
       </c>
       <c r="C18">
+        <f t="shared" si="2"/>
         <v>713</v>
       </c>
       <c r="D18">
+        <f t="shared" si="3"/>
         <v>729</v>
       </c>
       <c r="E18">
+        <f t="shared" si="4"/>
         <v>755</v>
       </c>
       <c r="F18">
+        <f t="shared" si="5"/>
         <v>786</v>
       </c>
       <c r="G18">
+        <f t="shared" si="6"/>
         <v>825</v>
       </c>
       <c r="H18">
+        <f t="shared" si="7"/>
         <v>863</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K18">
+        <v>71.3</v>
+      </c>
+      <c r="L18">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="M18">
+        <v>75.5</v>
+      </c>
+      <c r="N18">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="O18">
+        <v>82.5</v>
+      </c>
+      <c r="P18">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1116,25 +1510,52 @@
         <v>41</v>
       </c>
       <c r="C19">
+        <f t="shared" si="2"/>
         <v>425</v>
       </c>
       <c r="D19">
+        <f t="shared" si="3"/>
         <v>425</v>
       </c>
       <c r="E19">
+        <f t="shared" si="4"/>
         <v>425</v>
       </c>
       <c r="F19">
+        <f t="shared" si="5"/>
         <v>425</v>
       </c>
       <c r="G19">
+        <f t="shared" si="6"/>
         <v>425</v>
       </c>
       <c r="H19">
+        <f t="shared" si="7"/>
         <v>425</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J19" t="s">
+        <v>154</v>
+      </c>
+      <c r="K19">
+        <v>42.5</v>
+      </c>
+      <c r="L19">
+        <v>42.5</v>
+      </c>
+      <c r="M19">
+        <v>42.5</v>
+      </c>
+      <c r="N19">
+        <v>42.5</v>
+      </c>
+      <c r="O19">
+        <v>42.5</v>
+      </c>
+      <c r="P19">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1142,25 +1563,52 @@
         <v>43</v>
       </c>
       <c r="C20">
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
       <c r="D20">
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
       <c r="E20">
-        <v>54</v>
+        <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="F20">
-        <v>54</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="G20">
-        <v>54</v>
+        <f t="shared" si="6"/>
+        <v>48</v>
       </c>
       <c r="H20">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v>48</v>
+      </c>
+      <c r="J20" t="s">
+        <v>155</v>
+      </c>
+      <c r="K20">
+        <v>5.4</v>
+      </c>
+      <c r="L20">
+        <v>5.4</v>
+      </c>
+      <c r="M20">
+        <v>4.8</v>
+      </c>
+      <c r="N20">
+        <v>4.8</v>
+      </c>
+      <c r="O20">
+        <v>4.8</v>
+      </c>
+      <c r="P20">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1168,25 +1616,52 @@
         <v>45</v>
       </c>
       <c r="C21">
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="D21">
+        <f t="shared" si="3"/>
         <v>76</v>
       </c>
       <c r="E21">
+        <f t="shared" si="4"/>
         <v>79</v>
       </c>
       <c r="F21">
+        <f t="shared" si="5"/>
         <v>75</v>
       </c>
       <c r="G21">
+        <f t="shared" si="6"/>
         <v>75</v>
       </c>
       <c r="H21">
+        <f t="shared" si="7"/>
         <v>75</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J21" t="s">
+        <v>156</v>
+      </c>
+      <c r="K21">
+        <v>8.6</v>
+      </c>
+      <c r="L21">
+        <v>7.6</v>
+      </c>
+      <c r="M21">
+        <v>7.9</v>
+      </c>
+      <c r="N21">
+        <v>7.5</v>
+      </c>
+      <c r="O21">
+        <v>7.5</v>
+      </c>
+      <c r="P21">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1194,25 +1669,52 @@
         <v>47</v>
       </c>
       <c r="C22">
+        <f t="shared" si="2"/>
         <v>520</v>
       </c>
       <c r="D22">
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="E22">
+        <f t="shared" si="4"/>
         <v>561</v>
       </c>
       <c r="F22">
+        <f t="shared" si="5"/>
         <v>582</v>
       </c>
       <c r="G22">
+        <f t="shared" si="6"/>
         <v>603</v>
       </c>
       <c r="H22">
+        <f t="shared" si="7"/>
         <v>629</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>157</v>
+      </c>
+      <c r="K22">
+        <v>52</v>
+      </c>
+      <c r="L22">
+        <v>54</v>
+      </c>
+      <c r="M22">
+        <v>56.1</v>
+      </c>
+      <c r="N22">
+        <v>58.2</v>
+      </c>
+      <c r="O22">
+        <v>60.3</v>
+      </c>
+      <c r="P22">
+        <v>62.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -1220,25 +1722,52 @@
         <v>49</v>
       </c>
       <c r="C23">
+        <f t="shared" si="2"/>
         <v>543</v>
       </c>
       <c r="D23">
+        <f t="shared" si="3"/>
         <v>564</v>
       </c>
       <c r="E23">
+        <f t="shared" si="4"/>
         <v>585</v>
       </c>
       <c r="F23">
+        <f t="shared" si="5"/>
         <v>606</v>
       </c>
       <c r="G23">
+        <f t="shared" si="6"/>
         <v>627</v>
       </c>
       <c r="H23">
+        <f t="shared" si="7"/>
         <v>653</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>158</v>
+      </c>
+      <c r="K23">
+        <v>54.3</v>
+      </c>
+      <c r="L23">
+        <v>56.4</v>
+      </c>
+      <c r="M23">
+        <v>58.5</v>
+      </c>
+      <c r="N23">
+        <v>60.6</v>
+      </c>
+      <c r="O23">
+        <v>62.7</v>
+      </c>
+      <c r="P23">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1246,25 +1775,52 @@
         <v>51</v>
       </c>
       <c r="C24">
+        <f t="shared" si="2"/>
         <v>370</v>
       </c>
       <c r="D24">
+        <f t="shared" si="3"/>
         <v>382</v>
       </c>
       <c r="E24">
+        <f t="shared" si="4"/>
         <v>394</v>
       </c>
       <c r="F24">
+        <f t="shared" si="5"/>
         <v>406</v>
       </c>
       <c r="G24">
+        <f t="shared" si="6"/>
         <v>418</v>
       </c>
       <c r="H24">
+        <f t="shared" si="7"/>
         <v>430</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24">
+        <v>37</v>
+      </c>
+      <c r="L24">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="M24">
+        <v>39.4</v>
+      </c>
+      <c r="N24">
+        <v>40.6</v>
+      </c>
+      <c r="O24">
+        <v>41.8</v>
+      </c>
+      <c r="P24">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1272,25 +1828,52 @@
         <v>53</v>
       </c>
       <c r="C25">
+        <f t="shared" si="2"/>
         <v>361</v>
       </c>
       <c r="D25">
+        <f t="shared" si="3"/>
         <v>373</v>
       </c>
       <c r="E25">
+        <f t="shared" si="4"/>
         <v>386</v>
       </c>
       <c r="F25">
+        <f t="shared" si="5"/>
         <v>398</v>
       </c>
       <c r="G25">
+        <f t="shared" si="6"/>
         <v>410</v>
       </c>
       <c r="H25">
+        <f t="shared" si="7"/>
         <v>422</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>160</v>
+      </c>
+      <c r="K25">
+        <v>36.1</v>
+      </c>
+      <c r="L25">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="M25">
+        <v>38.6</v>
+      </c>
+      <c r="N25">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="O25">
+        <v>41</v>
+      </c>
+      <c r="P25">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1298,25 +1881,52 @@
         <v>55</v>
       </c>
       <c r="C26">
+        <f t="shared" si="2"/>
         <v>590</v>
       </c>
       <c r="D26">
+        <f t="shared" si="3"/>
         <v>605</v>
       </c>
       <c r="E26">
+        <f t="shared" si="4"/>
         <v>630</v>
       </c>
       <c r="F26">
+        <f t="shared" si="5"/>
         <v>665</v>
       </c>
       <c r="G26">
+        <f t="shared" si="6"/>
         <v>710</v>
       </c>
       <c r="H26">
+        <f t="shared" si="7"/>
         <v>755</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>150</v>
+      </c>
+      <c r="K26">
+        <v>59</v>
+      </c>
+      <c r="L26">
+        <v>60.5</v>
+      </c>
+      <c r="M26">
+        <v>63</v>
+      </c>
+      <c r="N26">
+        <v>66.5</v>
+      </c>
+      <c r="O26">
+        <v>71</v>
+      </c>
+      <c r="P26">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1324,25 +1934,52 @@
         <v>57</v>
       </c>
       <c r="C27">
+        <f t="shared" si="2"/>
         <v>790</v>
       </c>
       <c r="D27">
+        <f t="shared" si="3"/>
         <v>805</v>
       </c>
       <c r="E27">
+        <f t="shared" si="4"/>
         <v>830</v>
       </c>
       <c r="F27">
+        <f t="shared" si="5"/>
         <v>865</v>
       </c>
       <c r="G27">
+        <f t="shared" si="6"/>
         <v>910</v>
       </c>
       <c r="H27">
+        <f t="shared" si="7"/>
         <v>955</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>151</v>
+      </c>
+      <c r="K27">
+        <v>79</v>
+      </c>
+      <c r="L27">
+        <v>80.5</v>
+      </c>
+      <c r="M27">
+        <v>83</v>
+      </c>
+      <c r="N27">
+        <v>86.5</v>
+      </c>
+      <c r="O27">
+        <v>91</v>
+      </c>
+      <c r="P27">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1350,7 +1987,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -1375,16 +2012,70 @@
       <c r="H29">
         <v>110</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J29" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K29">
+        <f>K22/TAN(K10*PI()/180)</f>
+        <v>13.448114386506299</v>
+      </c>
+      <c r="L29">
+        <f t="shared" ref="L29:P29" si="8">L22/TAN(L10*PI()/180)</f>
+        <v>14.570318222166927</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="8"/>
+        <v>15.768998826048744</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="8"/>
+        <v>17.018871010363355</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="8"/>
+        <v>18.320540767865218</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="8"/>
+        <v>19.832293820488072</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>60</v>
       </c>
       <c r="B30" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J30" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K30">
+        <f>K29+K24</f>
+        <v>50.448114386506298</v>
+      </c>
+      <c r="L30">
+        <f t="shared" ref="L30:P30" si="9">L29+L24</f>
+        <v>52.770318222166928</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="9"/>
+        <v>55.168998826048743</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="9"/>
+        <v>57.618871010363357</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="9"/>
+        <v>60.120540767865215</v>
+      </c>
+      <c r="P30">
+        <f t="shared" si="9"/>
+        <v>62.832293820488076</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1409,8 +2100,35 @@
       <c r="H31">
         <v>700</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J31" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K31">
+        <f>K12</f>
+        <v>50.7</v>
+      </c>
+      <c r="L31">
+        <f t="shared" ref="L31:P31" si="10">L12</f>
+        <v>53</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="10"/>
+        <v>55.3</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="10"/>
+        <v>57.7</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="10"/>
+        <v>60.2</v>
+      </c>
+      <c r="P31">
+        <f t="shared" si="10"/>
+        <v>62.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -1520,6 +2238,9 @@
       </c>
       <c r="B37" t="s">
         <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">

--- a/data/gravel/Argon 18 Dark Matter 2025.xlsx
+++ b/data/gravel/Argon 18 Dark Matter 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC893F3-0A85-1C4D-95AC-F23EDEC30B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833892AB-AA63-0E4F-9E80-86AEE159E28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30480" yWindow="-28300" windowWidth="33620" windowHeight="20020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27620" yWindow="-28300" windowWidth="33620" windowHeight="20020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1139,7 +1139,7 @@
         <v>27</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C10:C27" si="2">K12*10</f>
+        <f t="shared" ref="C12:C27" si="2">K12*10</f>
         <v>507</v>
       </c>
       <c r="D12">
